--- a/output/pdf_financials_xlsx/SAE.xlsx
+++ b/output/pdf_financials_xlsx/SAE.xlsx
@@ -431,6 +431,27 @@
   </sheetPr>
   <dimension ref="A1:S135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAE.xlsx
+++ b/output/pdf_financials_xlsx/SAE.xlsx
@@ -7500,10 +7500,10 @@
         <v>-0.01</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.065562</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.044966</v>
       </c>
       <c r="N103" s="3" t="n">
         <v>0</v>
@@ -56806,7 +56806,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -59130,7 +59134,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAE.xlsx
+++ b/output/pdf_financials_xlsx/SAE.xlsx
@@ -1235,22 +1235,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001371</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004151</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002509</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002433</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002172</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -2474,22 +2474,22 @@
         <v>-0.488782</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.042149</v>
+        <v>-1.040778</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.051919</v>
+        <v>-1.047768</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.494652</v>
+        <v>-0.492143</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.6667960000000001</v>
+        <v>-0.664363</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.240792</v>
+        <v>-0.23862</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.348501</v>
+        <v>-0.348442</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2636,22 +2636,22 @@
         <v>-0.488782</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.042149</v>
+        <v>-1.040778</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.051919</v>
+        <v>-1.047768</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.494652</v>
+        <v>-0.492143</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.6667960000000001</v>
+        <v>-0.664363</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.240792</v>
+        <v>-0.23862</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.348501</v>
+        <v>-0.348442</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -10210,7 +10210,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -20052,7 +20056,11 @@
           <t>Reclamation deposit 11</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -25970,7 +25978,11 @@
           <t>Reclamation deposit 10</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -30282,7 +30294,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -47126,7 +47142,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -54050,7 +54070,11 @@
           <t>Reclamation deposits 16</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -57758,7 +57782,11 @@
           <t>Reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -59980,7 +60008,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -70780,7 +70812,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -70880,7 +70912,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -74046,7 +74078,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -75302,7 +75334,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAE.xlsx
+++ b/output/pdf_financials_xlsx/SAE.xlsx
@@ -2543,10 +2543,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -7279,10 +7277,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -7407,10 +7403,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -7598,10 +7592,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -7789,10 +7781,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7854,10 +7844,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -7919,10 +7907,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7984,10 +7970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -8049,10 +8033,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -8114,10 +8096,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -8179,10 +8159,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -8244,10 +8222,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -8309,10 +8285,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -8374,10 +8348,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -8439,10 +8411,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -8581,10 +8551,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -8646,10 +8614,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -8711,10 +8677,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -8776,10 +8740,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -8841,10 +8803,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8906,10 +8866,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8971,10 +8929,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -9133,10 +9089,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -9275,10 +9229,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>-0.060146</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>-0.060146</v>
@@ -9340,10 +9292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -9405,10 +9355,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.737188</v>
@@ -9470,10 +9418,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>-0.060146</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.677042</v>
@@ -9535,10 +9481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -67424,7 +67368,11 @@
           <t>Cash and cash equivalents (bank overdraft), end of year $</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -69978,7 +69926,11 @@
           <t>Cash and cash equivalents (bank overdraft), end of year $</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAE.xlsx
+++ b/output/pdf_financials_xlsx/SAE.xlsx
@@ -2178,15 +2178,11 @@
       <c r="L23" s="3" t="n">
         <v>-2.619043</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>-8.007165000000001</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>3.748291</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-10.139585</v>
@@ -2200,10 +2196,8 @@
       <c r="R23" s="3" t="n">
         <v>-6.246302</v>
       </c>
-      <c r="S23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S23" s="3" t="n">
+        <v>18.400959</v>
       </c>
     </row>
     <row r="24">
@@ -7238,15 +7232,11 @@
       <c r="L99" s="3" t="n">
         <v>-2.619043</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>-8.007165000000001</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>3.748291</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-10.139585</v>
@@ -7260,10 +7250,8 @@
       <c r="R99" s="3" t="n">
         <v>-6.246302</v>
       </c>
-      <c r="S99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S99" s="3" t="n">
+        <v>18.400959</v>
       </c>
     </row>
     <row r="100">
@@ -7998,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.072779</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -8007,13 +7995,13 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.234409</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.139132</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006035</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -8259,10 +8247,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>1.527968</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.974675</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -9509,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.072779</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -9518,13 +9506,13 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.234409</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.139132</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006035</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -9574,7 +9562,7 @@
         <v>-0.451187</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.960725</v>
+        <v>-2.033504</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-5.910899</v>
@@ -9583,13 +9571,13 @@
         <v>-5.658324</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-9.833410000000001</v>
+        <v>-10.067819</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-13.621436</v>
+        <v>-13.760568</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-10.392349</v>
+        <v>-10.398384</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-6.17313</v>
@@ -45038,7 +45026,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -48538,7 +48530,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -50310,7 +50306,11 @@
           <t>Proceeds from sale of marketable securities 6</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -50724,7 +50724,11 @@
           <t>Proceeds from issuance of shares pursuant to private placement 12</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -51256,7 +51260,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -57410,7 +57418,11 @@
           <t>Purchase of equipment 11</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -59740,7 +59752,11 @@
           <t>Purchase of equipment 10</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -66950,7 +66966,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
